--- a/output/pdf_financials_xlsx/MDX.xlsx
+++ b/output/pdf_financials_xlsx/MDX.xlsx
@@ -2400,55 +2400,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.057982</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.016911</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.016911</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.058705</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.016051</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.192277</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.003978</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.062754</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.207553</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.09625599999999999</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.038944</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.01192</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.106771</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.142496</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.138185</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.15829</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.018739</v>
       </c>
     </row>
     <row r="35">
@@ -2516,55 +2516,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.057982</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.016911</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.016911</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.058705</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.016051</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.192277</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.003978</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.062754</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.207553</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.09625599999999999</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.038944</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.01192</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.106771</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.142496</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.138185</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.15829</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.018739</v>
       </c>
     </row>
     <row r="37">
@@ -3212,55 +3212,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.164932</v>
+        <v>0.10695</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.048744</v>
+        <v>0.031833</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.048744</v>
+        <v>0.031833</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.09571499999999999</v>
+        <v>0.03701</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.027201</v>
+        <v>0.01115</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.209603</v>
+        <v>0.017326</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.050416</v>
+        <v>0.046438</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.078807</v>
+        <v>0.016053</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.232202</v>
+        <v>0.024649</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.164825</v>
+        <v>0.068569</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.073395</v>
+        <v>0.034451</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.059491</v>
+        <v>0.047571</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.160579</v>
+        <v>0.053808</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.195198</v>
+        <v>0.052702</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.259161</v>
+        <v>0.120976</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.438764</v>
+        <v>0.280474</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.200244</v>
+        <v>0.181505</v>
       </c>
     </row>
     <row r="49">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13507,7 +13507,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -36449,7 +36449,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">

--- a/output/pdf_financials_xlsx/MDX.xlsx
+++ b/output/pdf_financials_xlsx/MDX.xlsx
@@ -2109,13 +2109,13 @@
         <v>0.002</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.015044</v>
+        <v>1.420507</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.060563</v>
+        <v>0.068327</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.034</v>
+        <v>0.04229</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0.026</v>
@@ -2167,13 +2167,13 @@
         <v>-2.557007</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.97753</v>
+        <v>0.427933</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.807526</v>
+        <v>-0.799762</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.505224</v>
+        <v>-0.496934</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-1.866345</v>
@@ -2225,13 +2225,13 @@
         <v>-566.4928274716144</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-148.7058802053067</v>
+        <v>65.09892630803915</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-92.54421350838429</v>
+        <v>-91.65444243763351</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-69.37164795149158</v>
+        <v>-68.23335887275054</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-321.9806950806097</v>
@@ -6316,37 +6316,37 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.026926</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.068327</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.090182</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.090182</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.090182</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.090182</v>
       </c>
       <c r="N100" s="3" t="n">
         <v>0</v>
@@ -23851,7 +23851,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -27605,7 +27605,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -31316,7 +31320,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -32522,7 +32530,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -51885,7 +51893,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E442" t="inlineStr">
         <is>
           <t>-</t>
@@ -51986,7 +51998,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -53287,7 +53299,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -53388,7 +53400,11 @@
           <t>Depreciation of property, plant and equipment total</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MDX.xlsx
+++ b/output/pdf_financials_xlsx/MDX.xlsx
@@ -1560,11 +1560,15 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>-2.766736</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>-2.559007</v>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.992574</v>
@@ -1619,10 +1623,10 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-0.007109</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-0.005103</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -2757,10 +2761,10 @@
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.006076</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.003052</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>0</v>
@@ -2815,10 +2819,10 @@
         <v>0.070595</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.106504</v>
+        <v>0.11258</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.12745</v>
+        <v>0.130502</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>0.082167</v>
@@ -3221,10 +3225,10 @@
         <v>0.031833</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.03701</v>
+        <v>0.030934</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.01115</v>
+        <v>0.008097999999999999</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.017326</v>
@@ -4206,13 +4210,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.650762</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>1.115162</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.062821</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>4.199648</v>
@@ -4380,16 +4384,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.564821</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>1.440374</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>1.997806</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>2.337419</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>0</v>
@@ -4438,7 +4442,7 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0</v>
+        <v>1.215583</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>2.736264</v>
@@ -4447,7 +4451,7 @@
         <v>3.263876</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>4.199648</v>
+        <v>6.537067</v>
       </c>
       <c r="F68" s="3" t="n">
         <v>3.985297</v>
@@ -4853,7 +4857,7 @@
         <v>0.897435</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.779394</v>
+        <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
         <v>0.950512</v>
@@ -6255,10 +6259,10 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>-2.766736</v>
+        <v>-2.759627</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>-2.559007</v>
+        <v>-2.553904</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>-0.992574</v>
@@ -6731,7 +6735,7 @@
         <v>0</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="G107" s="3" t="n">
         <v>0.035722</v>
@@ -7250,7 +7254,7 @@
         <v>0</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.260485</v>
       </c>
       <c r="F116" s="3" t="n">
         <v>0</v>
@@ -7262,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.27701</v>
       </c>
       <c r="J116" s="3" t="n">
         <v>0</v>
@@ -25510,7 +25514,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -27009,7 +27017,11 @@
           <t>Share-based payments expense</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -28710,7 +28722,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -32334,7 +32350,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E245" s="5" t="n">
         <v>-2.759627</v>
       </c>
@@ -54695,7 +54715,11 @@
           <t>Loss from discontinued operations</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E470" s="5" t="n">
         <v>-0.007109</v>
       </c>
